--- a/src/test/output_test/Total_ROI/Histo_total_stats.xlsx
+++ b/src/test/output_test/Total_ROI/Histo_total_stats.xlsx
@@ -522,64 +522,64 @@
         <v>23</v>
       </c>
       <c r="C2">
-        <v>0.97699999809265</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0.97699999809265</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2">
-        <v>125256</v>
+        <v>119508</v>
       </c>
       <c r="G2">
-        <v>358681.4518715271</v>
+        <v>358524</v>
       </c>
       <c r="H2">
-        <v>358.6814518715271</v>
+        <v>358.524</v>
       </c>
       <c r="I2">
-        <v>-1000</v>
+        <v>-997</v>
       </c>
       <c r="J2">
-        <v>723</v>
+        <v>746</v>
       </c>
       <c r="K2">
-        <v>-46.88272018905282</v>
+        <v>-47.26163938815812</v>
       </c>
       <c r="L2">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M2">
-        <v>1189</v>
+        <v>1146</v>
       </c>
       <c r="N2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O2">
-        <v>231.0688366094062</v>
+        <v>230.5889598962698</v>
       </c>
       <c r="P2">
-        <v>-2.161037398624141</v>
+        <v>-2.163965571310381</v>
       </c>
       <c r="Q2">
-        <v>3.644312331148924</v>
+        <v>3.653541281546855</v>
       </c>
       <c r="R2">
-        <v>-434</v>
+        <v>-433</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2">
         <v>69</v>
       </c>
       <c r="U2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V2">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
